--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_921_Honduras_Caribbean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_921_Honduras_Caribbean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb29993dc99394089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf8395883f0364486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra7167a569ede4c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R17b34e00e874479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb4abafde965a4637"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6312eb52c63d40cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Raf0ed862faa246a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R29a8a422555c4fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc7dedf97ea3747a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R441df74ab9724bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5773ae30ed344926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd62232a562f94637"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ921CommercialTable" displayName="EEZ921CommercialTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ921CommercialTable" displayName="EEZ921CommercialTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ921FunctionalTable" displayName="EEZ921FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ921FunctionalTable" displayName="EEZ921FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ921ValidationTable" displayName="EEZ921ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ921ValidationTable" displayName="EEZ921ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6590,7 +6544,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5304637aee604311"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8354b165d6b43dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6600,20 +6554,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6621,390 +6565,136 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14094.735128571798</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2419044041213905</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>174.54379089505383</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14094.735128571798</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>208.2102765244279</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$89,A2,'Species'!$U$2:$U$89))</x:f>
-        <x:v>2934668.698658502</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2419044041213905</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>174.54379089505383</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2460148.5010026055</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>474520.19765589666</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.192882745680804</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.19288274568080396</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>631.3609827934</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.1663709571837133</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>14.668001887820639</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>631.3609827934</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>14.805639274042043</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$89,A3,'Species'!$U$2:$U$89))</x:f>
-        <x:v>9347.702962943746</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.1663709571837133</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>14.668001887820639</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>9260.804087509885</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>86.89887543386067</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0093835129879338</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009383512987933934</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3648.377948866799</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.375184415996645</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>237.23808842626377</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3648.377948866799</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>279.8191104468361</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$89,A4,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1020885.8722257602</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.375184415996645</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>237.23808842626377</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>865534.2104456925</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>155351.66178006772</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.17948644883727</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.17948644883727005</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2742.7289138968</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.795959529184588</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>625.1144372120975</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2742.7289138968</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1073.4177985515946</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$89,A5,'Species'!$U$2:$U$89))</x:f>
-        <x:v>2944094.032778909</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.795959529184588</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>625.1144372120975</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1714519.4414359455</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1229574.5913429635</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.717154067563777</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7171540675637772</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>25.160042372099998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.15</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1412.5375446227554</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>25.160042372099998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$89,A6,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>35539.504474890615</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.15</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>35539.504474890615</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>99.53219305110001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.408466055846678</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2561.3330642612696</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>99.53219305110001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2577.6617024526904</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$89,A7,'Species'!$U$2:$U$89))</x:f>
-        <x:v>256560.3221889483</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.408466055846678</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2561.3330642612696</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>254935.09702021824</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1625.225168730074</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0063750546226327</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.006375054622632763</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e6c5638a324fec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0e0736dec684b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7014,20 +6704,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7035,930 +6715,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2997.66</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2997.66</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$89,A2,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>864534.58756625</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>864534.58756625</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>13.1269696804</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.58</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>3801.8939632056126</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>13.1269696804</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>3801.8939632056126</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$89,A3,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>49907.34678309587</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.58</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>3801.8939632056126</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>49907.34678309587</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10.3480357258</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.17</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1479.1083881682073</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10.3480357258</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1479.1083881682073</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$89,A4,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15305.866443095065</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.17</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1479.1083881682073</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>15305.866443095065</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>37.920931789</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7088483652797612</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>511.5032120678307</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>37.920931789</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>520.7667108034352</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$89,A5,'Species'!$U$2:$U$89))</x:f>
-        <x:v>19747.958918358956</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7088483652797612</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>511.5032120678307</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>19396.67841467861</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>351.28050368034746</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0181103432335359</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.018110343233535945</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>272.4621149713</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.3909335613790805</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2459.9912444777306</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>272.4621149713</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2511.6009760108313</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$89,A6,'Species'!$U$2:$U$89))</x:f>
-        <x:v>684316.1138878925</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.3909335613790805</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2459.9912444777306</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>670254.4172812828</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>14061.696606609621</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0209796403336622</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.020979640333662147</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>212.1031409413</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6421805143372907</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>438.71301078034384</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>212.1031409413</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1325.3924595169776</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$89,A7,'Species'!$U$2:$U$89))</x:f>
-        <x:v>281119.9036434658</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6421805143372907</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>438.71301078034384</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>93052.40755832534</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>188067.49608514045</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>3.0210922105079283</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>2.0210922105079288</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25.160042372099998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.15</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1412.5375446227554</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25.160042372099998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$89,A8,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>35539.504474890615</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.15</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1412.5375446227554</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>35539.504474890615</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>12953.2304370809</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.269706767508149</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>186.0830293254826</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>12953.2304370809</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>217.28858216991517</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$89,A9,'Species'!$U$2:$U$89))</x:f>
-        <x:v>2814589.0761934994</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.269706767508149</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>186.0830293254826</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2410376.359283059</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>404212.7169104405</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1676969305451823</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.16769693054518228</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>19.6904545207</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1513.5612484362073</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>19.6904545207</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$89,A10,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>29802.708926627056</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>29802.708926627056</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>25.526125257199997</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.06</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1148.1536214968817</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>25.526125257199997</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$89,A11,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>29307.913156837196</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.06</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>29307.913156837196</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>769.310032716</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2172776564996983</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>164.92164443315056</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>769.310032716</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>208.66767244071187</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$89,A12,'Species'!$U$2:$U$89))</x:f>
-        <x:v>160530.1339121356</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2172776564996983</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>164.92164443315056</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>126875.87567444358</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>33654.25823769203</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2652534065975394</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2652534065975393</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1856.5195196204993</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.9092369343439386</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>811.40360768367</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1856.5195196204993</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1086.1216365390212</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$89,A13,'Species'!$U$2:$U$89))</x:f>
-        <x:v>2016406.0189168542</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.9092369343439386</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>811.40360768367</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1506386.635955227</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>510019.3829616271</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3385713672627044</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3385713672627045</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>824.8609827934</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1273428289456344</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>13.40734636097266</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>824.8609827934</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>13.67830846445756</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$89,A14,'Species'!$U$2:$U$89))</x:f>
-        <x:v>11282.702962943746</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1273428289456344</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>13.40734636097266</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>11059.196895963423</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>223.50606698032243</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.020209972666451</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.02020997266645117</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1141.5046914908999</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.926416940663148</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>84.41447827749066</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1141.5046914908999</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>105.19415588924892</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$89,A15,'Species'!$U$2:$U$89))</x:f>
-        <x:v>120079.62246500271</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.926416940663148</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>84.41447827749066</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>96359.52298351224</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>23720.09948149047</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2461624834480463</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.2461624834480463</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5.1946689083</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.59</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>389.04514499428046</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5.1946689083</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$89,A16,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2020.960718626854</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>2020.960718626854</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>77.27706168419999</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.300728186493464</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>199.861060023763</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>77.27706168419999</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>861.9079564977271</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$89,A17,'Species'!$U$2:$U$89))</x:f>
-        <x:v>66605.71432037762</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.300728186493464</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>199.861060023763</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>15444.675463725931</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>51161.03885665169</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>4.312535700527398</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>3.312535700527398</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e94f9daae6846b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8c290a379a9424a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8133,7 +7209,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8232,7 +7308,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>7201096.133289952</x:v>
+        <x:v>5339937.558466862</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8246,7 +7322,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>7201096.133289953</x:v>
+        <x:v>5975624.65757964</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8260,7 +7336,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-9.313225746154785e-10</x:v>
+        <x:v>-1861158.5748230908</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8274,7 +7350,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1225471.4757103128</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8285,9 +7361,9 @@
         <x:v>EEZ_921</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8299,47 +7375,19 @@
         <x:v>EEZ_921</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_921</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_921</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b80b4fe33a9461d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7065900f6614525"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8386,7 +7434,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
